--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G8" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2139,28 +2139,28 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
         <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
         <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -2190,7 +2190,7 @@
         <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="n">
         <v>8.6</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>110</v>
@@ -2211,22 +2211,22 @@
         <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
         <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO9" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP9" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR9" t="n">
         <v>55</v>
@@ -2241,13 +2241,13 @@
         <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>65</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
         <v>9.4</v>
@@ -2256,7 +2256,7 @@
         <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
@@ -2265,20 +2265,20 @@
         <v>13.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
         <v>75</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
         <v>44</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
         <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
@@ -2399,7 +2399,7 @@
         <v>40</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="n">
         <v>14.5</v>
@@ -2453,7 +2453,7 @@
         <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -2462,17 +2462,17 @@
         <v>18</v>
       </c>
       <c r="BE10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF10" t="n">
         <v>4</v>
       </c>
       <c r="BG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 00:58:24</t>
+          <t>2026-04-13 03:08:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G4" t="n">
         <v>3.45</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>6.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -1933,10 +1933,10 @@
         <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2139,10 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
         <v>2.12</v>
@@ -2151,16 +2151,16 @@
         <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
         <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -2181,10 +2181,10 @@
         <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>28</v>
@@ -2193,7 +2193,7 @@
         <v>140</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG9" t="n">
         <v>10</v>
@@ -2205,7 +2205,7 @@
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK9" t="n">
         <v>15</v>
@@ -2217,10 +2217,10 @@
         <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP9" t="n">
         <v>15.5</v>
@@ -2241,7 +2241,7 @@
         <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>65</v>
@@ -2262,7 +2262,7 @@
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>24</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>1.62</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q10" t="n">
         <v>1.31</v>
@@ -2348,7 +2348,7 @@
         <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
         <v>1.42</v>
@@ -2366,7 +2366,7 @@
         <v>55</v>
       </c>
       <c r="Y10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z10" t="n">
         <v>60</v>
@@ -2405,13 +2405,13 @@
         <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
         <v>44</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO10" t="n">
         <v>25</v>
@@ -2420,7 +2420,7 @@
         <v>44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AR10" t="n">
         <v>48</v>
@@ -2441,7 +2441,7 @@
         <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -2465,14 +2465,14 @@
         <v>36</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
         <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 03:08:31</t>
+          <t>2026-04-13 05:18:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
         <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>6.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="I7" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
         <v>1.22</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2121,10 +2121,10 @@
         <v>1.52</v>
       </c>
       <c r="H9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I9" t="n">
         <v>7.8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>4.7</v>
@@ -2142,13 +2142,13 @@
         <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
         <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
         <v>1.45</v>
@@ -2160,7 +2160,7 @@
         <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>24</v>
@@ -2184,19 +2184,19 @@
         <v>8.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF9" t="n">
         <v>8.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
         <v>25</v>
@@ -2205,7 +2205,7 @@
         <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK9" t="n">
         <v>15</v>
@@ -2229,10 +2229,10 @@
         <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS9" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2265,7 +2265,7 @@
         <v>14</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
         <v>75</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>
@@ -2318,13 +2318,13 @@
         <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2333,10 +2333,10 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P10" t="n">
         <v>3.95</v>
@@ -2345,13 +2345,13 @@
         <v>1.31</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
         <v>3.15</v>
@@ -2366,7 +2366,7 @@
         <v>55</v>
       </c>
       <c r="Y10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z10" t="n">
         <v>60</v>
@@ -2378,25 +2378,25 @@
         <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
         <v>20</v>
@@ -2405,10 +2405,10 @@
         <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN10" t="n">
         <v>4.3</v>
@@ -2420,7 +2420,7 @@
         <v>44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AR10" t="n">
         <v>48</v>
@@ -2432,7 +2432,7 @@
         <v>19</v>
       </c>
       <c r="AU10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
         <v>19.5</v>
@@ -2441,13 +2441,13 @@
         <v>40</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>32</v>
@@ -2465,14 +2465,14 @@
         <v>36</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
         <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 05:18:48</t>
+          <t>2026-04-13 07:28:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>3.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="I7" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.17</v>
       </c>
       <c r="G8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H8" t="n">
         <v>14</v>
@@ -1933,7 +1933,7 @@
         <v>20</v>
       </c>
       <c r="J8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="K8" t="n">
         <v>11</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2142,10 +2142,10 @@
         <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
         <v>1.87</v>
@@ -2160,7 +2160,7 @@
         <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>190</v>
       </c>
       <c r="AP9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
         <v>21</v>
@@ -2238,10 +2238,10 @@
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>65</v>
@@ -2250,7 +2250,7 @@
         <v>7.8</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>22</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I10" t="n">
         <v>4.8</v>
       </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K10" t="n">
         <v>5.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>1.31</v>
       </c>
       <c r="R10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
         <v>1.43</v>
@@ -2375,7 +2375,7 @@
         <v>120</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC10" t="n">
         <v>16</v>
@@ -2384,7 +2384,7 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
         <v>17.5</v>
@@ -2417,7 +2417,7 @@
         <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AQ10" t="n">
         <v>34</v>
@@ -2429,7 +2429,7 @@
         <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU10" t="n">
         <v>14</v>
@@ -2447,13 +2447,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -2465,14 +2465,14 @@
         <v>36</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG10" t="n">
         <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 07:28:55</t>
+          <t>2026-04-13 09:39:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -775,152 +775,152 @@
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
         <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G7" t="n">
         <v>6.8</v>
@@ -1736,13 +1736,13 @@
         <v>1.71</v>
       </c>
       <c r="I7" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -1927,16 +1927,16 @@
         <v>1.21</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
         <v>9.6</v>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>4.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -2121,16 +2121,16 @@
         <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2142,19 +2142,19 @@
         <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
         <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
@@ -2190,13 +2190,13 @@
         <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="n">
         <v>8.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
         <v>25</v>
@@ -2229,7 +2229,7 @@
         <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS9" t="n">
         <v>70</v>
@@ -2241,10 +2241,10 @@
         <v>9.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AX9" t="n">
         <v>7.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.62</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.63</v>
-      </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2333,13 +2333,13 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>1.31</v>
@@ -2351,7 +2351,7 @@
         <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U10" t="n">
         <v>3.15</v>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Y10" t="n">
         <v>40</v>
@@ -2372,7 +2372,7 @@
         <v>60</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
         <v>23</v>
@@ -2399,28 +2399,28 @@
         <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK10" t="n">
         <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
         <v>46</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AQ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR10" t="n">
         <v>48</v>
@@ -2429,13 +2429,13 @@
         <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>40</v>
@@ -2444,7 +2444,7 @@
         <v>15.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
@@ -2462,7 +2462,7 @@
         <v>18</v>
       </c>
       <c r="BE10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF10" t="n">
         <v>3.95</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 09:39:50</t>
+          <t>2026-04-13 11:50:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,19 +784,19 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G3" t="n">
         <v>2.06</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
@@ -987,13 +987,13 @@
         <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
         <v>2.6</v>
@@ -1163,159 +1163,159 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
         <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Slavia Praha B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1357,159 +1357,159 @@
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Sparta Prague B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1.82</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,378 +2101,1930 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 11:50:04</t>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Usti nad Labem</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MFK Chrudim</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MAS Taborsko</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FC Zbrojovka Brno</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zizkov</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Saudi 1st Division</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Al-Raed (KSA)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Al Orubah</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Slovenian Premier League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NK Celje</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Olimpija</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>230</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" t="n">
+        <v>21</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>44</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.61</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="H18" t="n">
         <v>4.9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="I18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>5.6</v>
       </c>
-      <c r="K10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.02</v>
       </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="N18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.1</v>
       </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="P18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1.31</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R18" t="n">
         <v>2.24</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S18" t="n">
         <v>1.76</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T18" t="n">
         <v>1.44</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U18" t="n">
         <v>3.15</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z18" t="n">
         <v>60</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS18" t="n">
         <v>40</v>
       </c>
-      <c r="Z10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AT18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>16</v>
       </c>
-      <c r="AD10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="BA18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB18" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BC18" t="n">
         <v>13</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BD18" t="n">
         <v>18</v>
       </c>
-      <c r="BE10" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-04-13 11:50:04</t>
+      <c r="BE18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:01:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.65</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -975,13 +975,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
         <v>1.51</v>
@@ -993,7 +993,7 @@
         <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
@@ -1002,7 +1002,7 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1145,76 +1145,76 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
         <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
         <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>18</v>
@@ -1223,7 +1223,7 @@
         <v>48</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG4" t="n">
         <v>19</v>
@@ -1253,16 +1253,16 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>12</v>
+        <v>1.84</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AT4" t="n">
         <v>2.14</v>
@@ -1274,41 +1274,41 @@
         <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AY4" t="n">
         <v>2.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.29</v>
@@ -1835,52 +1835,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.38</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ceske Budejovice</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2518,7 +2518,7 @@
         <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zizkov</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -2712,7 +2712,7 @@
         <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
         <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,22 +2915,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G14" t="n">
         <v>2.12</v>
@@ -3094,7 +3094,7 @@
         <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>230</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>2.78</v>
@@ -3115,13 +3115,13 @@
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
         <v>2.38</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
-        <v>1.71</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.83</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Sarpsborg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1.24</v>
+        <v>7.6</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P16" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,378 +3653,766 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.51</v>
+        <v>5.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>1.71</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>1.82</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>8.4</v>
+        <v>65</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW17" t="n">
         <v>15</v>
       </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>48</v>
-      </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>2.56</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>2.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>2.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>2.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>32</v>
+        <v>2.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>75</v>
+        <v>2.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>44</v>
+        <v>2.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 14:01:49</t>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="X18" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:12:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:12:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.6</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J18" t="n">
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J20" t="n">
         <v>5.6</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K20" t="n">
         <v>5.7</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="L20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M20" t="n">
         <v>1.02</v>
       </c>
-      <c r="N18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.1</v>
       </c>
-      <c r="P18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1.31</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="R20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.44</v>
       </c>
-      <c r="U18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="U20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X20" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS20" t="n">
         <v>40</v>
       </c>
-      <c r="Z18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AT20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX20" t="n">
         <v>16</v>
       </c>
-      <c r="AD18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AY20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD20" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="BE20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG20" t="n">
         <v>20</v>
       </c>
-      <c r="AM18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-04-13 14:01:49</t>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:12:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
         <v>1.98</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.84</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
         <v>3.1</v>
@@ -1160,7 +1160,7 @@
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1187,7 +1187,7 @@
         <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.01</v>
@@ -1196,10 +1196,10 @@
         <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1211,10 +1211,10 @@
         <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
         <v>18</v>
@@ -1253,16 +1253,16 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AT4" t="n">
         <v>2.14</v>
@@ -1274,41 +1274,41 @@
         <v>2.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AY4" t="n">
         <v>2.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.26</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q6" t="n">
         <v>1.26</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1751,13 +1751,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q7" t="n">
         <v>1.29</v>
@@ -1766,7 +1766,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
         <v>1.3</v>
@@ -1960,7 +1960,7 @@
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
         <v>1.38</v>
@@ -2154,7 +2154,7 @@
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
         <v>1.15</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.27</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
         <v>1.27</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -2924,13 +2924,13 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
         <v>2.78</v>
@@ -3106,7 +3106,7 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
         <v>3.75</v>
@@ -3124,7 +3124,7 @@
         <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
         <v>1.91</v>
@@ -3291,16 +3291,16 @@
         <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
         <v>2.2</v>
@@ -3312,10 +3312,10 @@
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>1.72</v>
@@ -3381,25 +3381,25 @@
         <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3411,10 +3411,10 @@
         <v>4.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -3423,13 +3423,13 @@
         <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
         <v>4.7</v>
@@ -3438,11 +3438,11 @@
         <v>7.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="O16" t="n">
         <v>1.06</v>
@@ -3509,7 +3509,7 @@
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S16" t="n">
         <v>1.66</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G17" t="n">
         <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.41</v>
@@ -3691,13 +3691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
@@ -3730,22 +3730,22 @@
         <v>13</v>
       </c>
       <c r="AA17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AC17" t="n">
         <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG17" t="n">
         <v>29</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>2.38</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>2.56</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -3885,10 +3885,10 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="P18" t="n">
         <v>4.5</v>
@@ -3897,16 +3897,16 @@
         <v>1.24</v>
       </c>
       <c r="R18" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
         <v>1.05</v>
@@ -3915,116 +3915,116 @@
         <v>5.9</v>
       </c>
       <c r="X18" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y18" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB18" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
         <v>36</v>
       </c>
       <c r="AD18" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>48</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.49</v>
+        <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1.58</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4064,16 +4064,16 @@
         <v>7.6</v>
       </c>
       <c r="I19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4085,10 +4085,10 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
@@ -4118,13 +4118,13 @@
         <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB19" t="n">
         <v>8.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>28</v>
@@ -4133,7 +4133,7 @@
         <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -4160,16 +4160,16 @@
         <v>7.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS19" t="n">
         <v>70</v>
@@ -4178,7 +4178,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
@@ -4193,7 +4193,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA19" t="n">
         <v>40</v>
@@ -4211,14 +4211,14 @@
         <v>75</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
         <v>5.2</v>
@@ -4276,22 +4276,22 @@
         <v>10</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="T20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U20" t="n">
         <v>3.2</v>
@@ -4303,7 +4303,7 @@
         <v>2.66</v>
       </c>
       <c r="X20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Y20" t="n">
         <v>42</v>
@@ -4318,7 +4318,7 @@
         <v>23</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
@@ -4327,13 +4327,13 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4351,13 +4351,13 @@
         <v>44</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AQ20" t="n">
         <v>36</v>
@@ -4366,7 +4366,7 @@
         <v>50</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
         <v>20</v>
@@ -4381,16 +4381,16 @@
         <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>18.5</v>
@@ -4402,17 +4402,17 @@
         <v>17.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 16:12:54</t>
+          <t>2026-04-13 18:21:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1169,10 +1169,10 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
         <v>1.69</v>
@@ -1187,10 +1187,10 @@
         <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V4" t="n">
         <v>1.48</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AR4" t="n">
         <v>1.87</v>
@@ -1265,13 +1265,13 @@
         <v>2.6</v>
       </c>
       <c r="AT4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU4" t="n">
         <v>2.14</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AV4" t="n">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AW4" t="n">
         <v>1.94</v>
@@ -1280,10 +1280,10 @@
         <v>2.12</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="BA4" t="n">
         <v>2.62</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,22 +1363,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,13 +1557,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
         <v>1.26</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,16 +1945,16 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.38</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2333,34 +2333,34 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.24</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2554,7 +2554,7 @@
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2697,46 +2697,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.79</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="H14" t="n">
         <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
         <v>5</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
@@ -3291,10 +3291,10 @@
         <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.34</v>
@@ -3312,7 +3312,7 @@
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3387,10 +3387,10 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.5</v>
@@ -3399,7 +3399,7 @@
         <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3408,22 +3408,22 @@
         <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX15" t="n">
         <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S16" t="n">
         <v>1.66</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G17" t="n">
         <v>6.6</v>
@@ -3700,7 +3700,7 @@
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
         <v>1.22</v>
@@ -3724,7 +3724,7 @@
         <v>15.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
         <v>13</v>
@@ -3736,7 +3736,7 @@
         <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -3775,10 +3775,10 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="AR17" t="n">
         <v>6.8</v>
@@ -3787,50 +3787,50 @@
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.34</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="AX17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY17" t="n">
         <v>2.5</v>
       </c>
-      <c r="AY17" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -3903,10 +3903,10 @@
         <v>1.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
         <v>1.05</v>
@@ -3984,7 +3984,7 @@
         <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
         <v>8.800000000000001</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4073,34 +4073,34 @@
         <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
         <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
         <v>1.14</v>
@@ -4109,7 +4109,7 @@
         <v>2.96</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
         <v>24</v>
@@ -4121,7 +4121,7 @@
         <v>260</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
@@ -4145,7 +4145,7 @@
         <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK19" t="n">
         <v>15</v>
@@ -4166,16 +4166,16 @@
         <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS19" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>9.800000000000001</v>
@@ -4187,7 +4187,7 @@
         <v>48</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
@@ -4196,13 +4196,13 @@
         <v>24</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BB19" t="n">
         <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>34</v>
@@ -4214,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
         <v>5.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>5.6</v>
@@ -4267,13 +4267,13 @@
         <v>5.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O20" t="n">
         <v>1.09</v>
@@ -4285,10 +4285,10 @@
         <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S20" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="T20" t="n">
         <v>1.43</v>
@@ -4297,10 +4297,10 @@
         <v>3.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X20" t="n">
         <v>55</v>
@@ -4315,7 +4315,7 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
         <v>16</v>
@@ -4327,7 +4327,7 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
@@ -4351,7 +4351,7 @@
         <v>44</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AO20" t="n">
         <v>24</v>
@@ -4381,16 +4381,16 @@
         <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
         <v>18.5</v>
@@ -4399,20 +4399,20 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
         <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 18:21:23</t>
+          <t>2026-04-13 20:29:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>6.6</v>
@@ -966,7 +966,7 @@
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -993,7 +993,7 @@
         <v>2.26</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
@@ -1002,7 +1002,7 @@
         <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1190,16 +1190,16 @@
         <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1211,7 +1211,7 @@
         <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1256,59 +1256,59 @@
         <v>2.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AR4" t="n">
         <v>1.87</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="AT4" t="n">
         <v>2.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="AV4" t="n">
         <v>1.82</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AY4" t="n">
         <v>1.83</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="BE4" t="n">
         <v>2.02</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
         <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="K7" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1754,19 +1754,19 @@
         <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1948,7 +1948,7 @@
         <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>5.1</v>
@@ -2324,7 +2324,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,13 +2333,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>1.58</v>
@@ -2348,7 +2348,7 @@
         <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2360,7 +2360,7 @@
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q11" t="n">
         <v>1.53</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.31</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S12" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
         <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,10 +3115,10 @@
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -3127,16 +3127,16 @@
         <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.6</v>
@@ -3303,16 +3303,16 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3390,7 +3390,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.5</v>
@@ -3414,7 +3414,7 @@
         <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -3423,7 +3423,7 @@
         <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>1.06</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P16" t="n">
         <v>3.75</v>
@@ -3509,134 +3509,134 @@
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T16" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I17" t="n">
         <v>1.83</v>
@@ -3700,7 +3700,7 @@
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.22</v>
@@ -3721,13 +3721,13 @@
         <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
         <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
         <v>26</v>
@@ -3736,7 +3736,7 @@
         <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
         <v>15.5</v>
@@ -3775,7 +3775,7 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.7</v>
@@ -3790,47 +3790,47 @@
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
@@ -3879,7 +3879,7 @@
         <v>11.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -3891,28 +3891,28 @@
         <v>1.08</v>
       </c>
       <c r="P18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S18" t="n">
         <v>1.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
         <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X18" t="n">
         <v>95</v>
@@ -3930,7 +3930,7 @@
         <v>21</v>
       </c>
       <c r="AC18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AD18" t="n">
         <v>60</v>
@@ -3945,7 +3945,7 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AI18" t="n">
         <v>140</v>
@@ -3963,34 +3963,34 @@
         <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AO18" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT18" t="n">
         <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
@@ -3999,10 +3999,10 @@
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -4011,20 +4011,20 @@
         <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
         <v>2.24</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4067,10 +4067,10 @@
         <v>8</v>
       </c>
       <c r="J19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K19" t="n">
         <v>4.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4082,7 +4082,7 @@
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
         <v>2.12</v>
@@ -4118,7 +4118,7 @@
         <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>8.199999999999999</v>
@@ -4145,7 +4145,7 @@
         <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK19" t="n">
         <v>15</v>
@@ -4172,7 +4172,7 @@
         <v>50</v>
       </c>
       <c r="AS19" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -4205,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
         <v>75</v>
@@ -4214,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
         <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
         <v>22</v>
@@ -4342,7 +4342,7 @@
         <v>19.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4399,20 +4399,20 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE20" t="n">
         <v>38</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
         <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 20:29:06</t>
+          <t>2026-04-13 22:36:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
         <v>1.97</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
         <v>2.56</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.4</v>
@@ -1169,7 +1169,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O4" t="n">
         <v>1.34</v>
@@ -1178,7 +1178,7 @@
         <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.21</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,22 +1363,22 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O5" t="n">
         <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="I6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
         <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="I7" t="n">
         <v>3.45</v>
@@ -1742,7 +1742,7 @@
         <v>2.48</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1760,13 +1760,13 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="K8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1954,13 +1954,13 @@
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
         <v>5.1</v>
@@ -2324,7 +2324,7 @@
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2360,7 +2360,7 @@
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.33</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -2730,13 +2730,13 @@
         <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
         <v>1.93</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3133,7 +3133,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
         <v>1.93</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H15" t="n">
         <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
@@ -3297,22 +3297,22 @@
         <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3387,10 +3387,10 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.5</v>
@@ -3399,7 +3399,7 @@
         <v>4.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3414,7 +3414,7 @@
         <v>9.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -3423,7 +3423,7 @@
         <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I17" t="n">
         <v>1.83</v>
@@ -3688,31 +3688,31 @@
         <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
         <v>2.2</v>
@@ -3721,116 +3721,116 @@
         <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>9</v>
       </c>
-      <c r="Z17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AW17" t="n">
-        <v>2.56</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.62</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.74</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.86</v>
+        <v>8.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.86</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>1.11</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H19" t="n">
         <v>7.6</v>
@@ -4070,7 +4070,7 @@
         <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4106,7 +4106,7 @@
         <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X19" t="n">
         <v>16</v>
@@ -4133,7 +4133,7 @@
         <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -4214,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>
@@ -4258,13 +4258,13 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K20" t="n">
         <v>5.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -4300,7 +4300,7 @@
         <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
         <v>55</v>
@@ -4330,10 +4330,10 @@
         <v>17.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4342,10 +4342,10 @@
         <v>19.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AM20" t="n">
         <v>44</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-13 22:36:44</t>
+          <t>2026-04-14 00:44:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>1.18</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -999,10 +999,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT4" t="n">
         <v>4.6</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AU4" t="n">
-        <v>1.69</v>
+        <v>3.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.82</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.96</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.89</v>
+        <v>5.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.83</v>
+        <v>4.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.99</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.99</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.96</v>
+        <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.99</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,10 +1387,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,22 +1557,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>2.48</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>7.8</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1760,13 +1760,13 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1948,19 +1948,19 @@
         <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
         <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2524,25 +2524,25 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
         <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,22 +3109,22 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.5</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3166,7 +3166,7 @@
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3303,16 +3303,16 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3336,13 +3336,13 @@
         <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
         <v>12.5</v>
@@ -3351,10 +3351,10 @@
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF15" t="n">
         <v>14.5</v>
@@ -3369,7 +3369,7 @@
         <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
@@ -3381,25 +3381,25 @@
         <v>95</v>
       </c>
       <c r="AN15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3411,10 +3411,10 @@
         <v>4.7</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -3423,26 +3423,26 @@
         <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.7</v>
       </c>
-      <c r="BF15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K16" t="n">
         <v>6.2</v>
@@ -3497,10 +3497,10 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
         <v>3.75</v>
@@ -3512,13 +3512,13 @@
         <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T16" t="n">
         <v>1.52</v>
       </c>
       <c r="U16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V16" t="n">
         <v>2.64</v>
@@ -3536,16 +3536,16 @@
         <v>18.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AC16" t="n">
         <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
@@ -3578,10 +3578,10 @@
         <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
         <v>17</v>
@@ -3593,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
         <v>13.5</v>
@@ -3605,10 +3605,10 @@
         <v>12.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>15.5</v>
@@ -3617,26 +3617,26 @@
         <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC16" t="n">
         <v>55</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.2</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>44</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="BG16" t="n">
         <v>3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="I17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3697,73 +3697,73 @@
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AC17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>4.3</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -3867,85 +3867,85 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="J18" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="O18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R18" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="X18" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Y18" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="Z18" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AA18" t="n">
-        <v>610</v>
+        <v>650</v>
       </c>
       <c r="AB18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AD18" t="n">
         <v>60</v>
       </c>
       <c r="AE18" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI18" t="n">
         <v>140</v>
@@ -3960,71 +3960,71 @@
         <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="AO18" t="n">
         <v>170</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>1.92</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>11.5</v>
+        <v>1.95</v>
       </c>
       <c r="AT18" t="n">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="BG18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4094,13 +4094,13 @@
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V19" t="n">
         <v>1.14</v>
@@ -4118,7 +4118,7 @@
         <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AB19" t="n">
         <v>8.199999999999999</v>
@@ -4133,7 +4133,7 @@
         <v>120</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -4187,7 +4187,7 @@
         <v>48</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
@@ -4196,7 +4196,7 @@
         <v>24</v>
       </c>
       <c r="BA19" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
         <v>12</v>
@@ -4214,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>
@@ -4285,10 +4285,10 @@
         <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T20" t="n">
         <v>1.43</v>
@@ -4300,7 +4300,7 @@
         <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="X20" t="n">
         <v>55</v>
@@ -4321,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>48</v>
@@ -4345,7 +4345,7 @@
         <v>13.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="n">
         <v>44</v>
@@ -4354,10 +4354,10 @@
         <v>4.1</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AQ20" t="n">
         <v>36</v>
@@ -4399,7 +4399,7 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BE20" t="n">
         <v>38</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 00:44:01</t>
+          <t>2026-04-14 02:51:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -951,46 +951,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>970</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.18</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>970</v>
+        <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -999,16 +999,16 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,34 +1017,34 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
@@ -1163,7 +1163,7 @@
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1172,10 +1172,10 @@
         <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
         <v>2.16</v>
@@ -1184,16 +1184,16 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.46</v>
@@ -1235,7 +1235,7 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
         <v>48</v>
@@ -1259,7 +1259,7 @@
         <v>4.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS4" t="n">
         <v>6.2</v>
@@ -1268,16 +1268,16 @@
         <v>4.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY4" t="n">
         <v>4.8</v>
@@ -1295,20 +1295,20 @@
         <v>6.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1357,13 +1357,13 @@
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1554,19 +1554,19 @@
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1575,16 +1575,16 @@
         <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K7" t="n">
-        <v>950</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -1766,7 +1766,7 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -1939,19 +1939,19 @@
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
         <v>1.31</v>
@@ -1963,16 +1963,16 @@
         <v>1.01</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2524,22 +2524,22 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
         <v>1.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
         <v>1.54</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
         <v>1.25</v>
@@ -2727,16 +2727,16 @@
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>2.54</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -2927,10 +2927,10 @@
         <v>1.24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3151,10 +3151,10 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3163,10 +3163,10 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
         <v>1000</v>
@@ -3193,31 +3193,31 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU14" t="n">
         <v>3.55</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY14" t="n">
         <v>3.75</v>
@@ -3226,29 +3226,29 @@
         <v>4.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -3303,28 +3303,28 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
         <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>1.72</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3336,13 +3336,13 @@
         <v>23</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB15" t="n">
         <v>12.5</v>
@@ -3351,10 +3351,10 @@
         <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF15" t="n">
         <v>14.5</v>
@@ -3369,7 +3369,7 @@
         <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
         <v>21</v>
@@ -3384,19 +3384,19 @@
         <v>11.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3408,41 +3408,41 @@
         <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
         <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
         <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG15" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H16" t="n">
         <v>1.45</v>
@@ -3485,13 +3485,13 @@
         <v>1.49</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K16" t="n">
         <v>6.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
@@ -3509,19 +3509,19 @@
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="T16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V16" t="n">
         <v>2.66</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.64</v>
       </c>
       <c r="W16" t="n">
         <v>1.13</v>
@@ -3530,31 +3530,31 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AB16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
         <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
         <v>17</v>
       </c>
       <c r="AF16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3566,7 +3566,7 @@
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
         <v>1000</v>
@@ -3575,25 +3575,25 @@
         <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
         <v>3.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
         <v>13.5</v>
@@ -3602,41 +3602,41 @@
         <v>10.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>29</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
         <v>3</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3697,73 +3697,73 @@
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>18.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL17" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="I18" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
         <v>11.5</v>
@@ -3885,46 +3885,46 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
         <v>1.07</v>
       </c>
       <c r="P18" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
         <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="X18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Y18" t="n">
         <v>110</v>
       </c>
       <c r="Z18" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AA18" t="n">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="AB18" t="n">
         <v>22</v>
@@ -3936,10 +3936,10 @@
         <v>60</v>
       </c>
       <c r="AE18" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
         <v>15</v>
@@ -3969,62 +3969,62 @@
         <v>170</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV18" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AW18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
         <v>5.1</v>
       </c>
       <c r="AY18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BD18" t="n">
         <v>6</v>
       </c>
-      <c r="BA18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>1.97</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4085,22 +4085,22 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
         <v>1.14</v>
@@ -4118,7 +4118,7 @@
         <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB19" t="n">
         <v>8.199999999999999</v>
@@ -4169,10 +4169,10 @@
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS19" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -4181,13 +4181,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
@@ -4196,29 +4196,29 @@
         <v>24</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BB19" t="n">
         <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G20" t="n">
         <v>1.61</v>
@@ -4258,7 +4258,7 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>5.5</v>
@@ -4285,10 +4285,10 @@
         <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T20" t="n">
         <v>1.43</v>
@@ -4306,7 +4306,7 @@
         <v>55</v>
       </c>
       <c r="Y20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z20" t="n">
         <v>60</v>
@@ -4315,7 +4315,7 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="n">
         <v>16</v>
@@ -4324,16 +4324,16 @@
         <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4354,7 +4354,7 @@
         <v>4.1</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP20" t="n">
         <v>46</v>
@@ -4363,16 +4363,16 @@
         <v>36</v>
       </c>
       <c r="AR20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS20" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AT20" t="n">
         <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>21</v>
@@ -4384,7 +4384,7 @@
         <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
@@ -4399,20 +4399,20 @@
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
         <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 02:51:15</t>
+          <t>2026-04-14 04:58:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
         <v>5.6</v>
@@ -984,7 +984,7 @@
         <v>2.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
@@ -993,7 +993,7 @@
         <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>1.01</v>
@@ -1002,7 +1002,7 @@
         <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
@@ -1059,10 +1059,10 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.65</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
         <v>3.85</v>
@@ -1071,50 +1071,50 @@
         <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="BE3" t="n">
         <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="BG3" t="n">
         <v>3.9</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="I4" t="n">
         <v>2.92</v>
@@ -1160,7 +1160,7 @@
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1175,19 +1175,19 @@
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
         <v>1.98</v>
@@ -1202,37 +1202,37 @@
         <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>12.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>46</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>65</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>9.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.24</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
         <v>1.78</v>
@@ -1581,16 +1581,16 @@
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1602,7 +1602,7 @@
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1730,167 +1730,167 @@
         <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>1.46</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.4</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.76</v>
@@ -1969,10 +1969,10 @@
         <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -2142,19 +2142,19 @@
         <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -2312,55 +2312,55 @@
         <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
         <v>1.01</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.24</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.09</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>1.54</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>1000</v>
@@ -2581,7 +2581,7 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
         <v>1000</v>
@@ -2605,68 +2605,68 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -2891,58 +2891,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.25</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.02</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.55</v>
+        <v>2.72</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1.33</v>
@@ -3118,7 +3118,7 @@
         <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
         <v>1.45</v>
@@ -3127,19 +3127,19 @@
         <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3154,10 +3154,10 @@
         <v>12</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3166,10 +3166,10 @@
         <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR14" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AS14" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.75</v>
+        <v>7.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE14" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE14" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF14" t="n">
-        <v>3.85</v>
+        <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3306,13 +3306,13 @@
         <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
         <v>1.49</v>
@@ -3324,7 +3324,7 @@
         <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3390,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4.4</v>
@@ -3414,7 +3414,7 @@
         <v>9.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
         <v>13.5</v>
@@ -3423,7 +3423,7 @@
         <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G16" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I16" t="n">
         <v>1.49</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -3509,13 +3509,13 @@
         <v>1.32</v>
       </c>
       <c r="R16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="T16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="U16" t="n">
         <v>2.68</v>
@@ -3524,25 +3524,25 @@
         <v>2.66</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
         <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -3551,37 +3551,37 @@
         <v>17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG16" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -3593,10 +3593,10 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3605,38 +3605,38 @@
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -3667,58 +3667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I17" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -3730,31 +3730,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP17" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4.9</v>
       </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4</v>
-      </c>
       <c r="AW17" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
         <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG17" t="n">
         <v>10.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
         <v>11.5</v>
@@ -3894,25 +3894,25 @@
         <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R18" t="n">
         <v>2.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X18" t="n">
         <v>100</v>
@@ -3921,13 +3921,13 @@
         <v>110</v>
       </c>
       <c r="Z18" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="n">
         <v>620</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="n">
         <v>29</v>
@@ -3945,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AI18" t="n">
         <v>140</v>
@@ -3963,68 +3963,68 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AO18" t="n">
         <v>170</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.94</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.97</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AV18" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4088,7 +4088,7 @@
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
@@ -4100,7 +4100,7 @@
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
         <v>1.14</v>
@@ -4109,7 +4109,7 @@
         <v>2.92</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
         <v>24</v>
@@ -4139,7 +4139,7 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>110</v>
@@ -4151,7 +4151,7 @@
         <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM19" t="n">
         <v>150</v>
@@ -4160,10 +4160,10 @@
         <v>7.4</v>
       </c>
       <c r="AO19" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
@@ -4214,11 +4214,11 @@
         <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>
@@ -4258,13 +4258,13 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -4285,7 +4285,7 @@
         <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
         <v>1.76</v>
@@ -4297,7 +4297,7 @@
         <v>3.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
         <v>2.64</v>
@@ -4306,7 +4306,7 @@
         <v>55</v>
       </c>
       <c r="Y20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z20" t="n">
         <v>60</v>
@@ -4315,16 +4315,16 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
         <v>16</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF20" t="n">
         <v>17</v>
@@ -4333,7 +4333,7 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4345,7 +4345,7 @@
         <v>13.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AM20" t="n">
         <v>44</v>
@@ -4366,10 +4366,10 @@
         <v>55</v>
       </c>
       <c r="AS20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4405,14 +4405,14 @@
         <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 04:58:26</t>
+          <t>2026-04-14 07:05:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
         <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
         <v>4.3</v>
@@ -963,7 +963,7 @@
         <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1145,100 +1145,100 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.47</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.46</v>
-      </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>55</v>
       </c>
-      <c r="AB4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>65</v>
-      </c>
       <c r="AK4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>65</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1363,34 +1363,34 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
         <v>19.5</v>
@@ -1405,10 +1405,10 @@
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>20</v>
@@ -1429,10 +1429,10 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>38</v>
@@ -1447,62 +1447,62 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF5" t="n">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY6" t="n">
         <v>4.2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AZ6" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4.1</v>
       </c>
-      <c r="BA6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1730,28 +1730,28 @@
         <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="I7" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
@@ -1763,10 +1763,10 @@
         <v>1.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
         <v>1.73</v>
@@ -1775,10 +1775,10 @@
         <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1853,7 +1853,7 @@
         <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AW7" t="n">
         <v>4.5</v>
@@ -1871,7 +1871,7 @@
         <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC7" t="n">
         <v>4.4</v>
@@ -1880,7 +1880,7 @@
         <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF7" t="n">
         <v>4.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -1921,28 +1921,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
         <v>3.3</v>
@@ -1954,25 +1954,25 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
         <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>3.9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.95</v>
       </c>
       <c r="AR8" t="n">
         <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT8" t="n">
         <v>3.45</v>
@@ -2053,38 +2053,38 @@
         <v>4.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
         <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
         <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BG8" t="n">
         <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2271,14 +2271,14 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG9" t="n">
         <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.08</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
         <v>5.1</v>
@@ -2324,7 +2324,7 @@
         <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
@@ -2333,16 +2333,16 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
         <v>1.46</v>
@@ -2354,10 +2354,10 @@
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.92</v>
@@ -2420,7 +2420,7 @@
         <v>3.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR10" t="n">
         <v>3.8</v>
@@ -2459,7 +2459,7 @@
         <v>3.55</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
         <v>4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>1.39</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
         <v>11.5</v>
@@ -2527,7 +2527,7 @@
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.22</v>
@@ -2542,7 +2542,7 @@
         <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T11" t="n">
         <v>1.92</v>
@@ -2554,7 +2554,7 @@
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2623,10 +2623,10 @@
         <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>4.5</v>
@@ -2635,10 +2635,10 @@
         <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.4</v>
@@ -2647,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="BC11" t="n">
         <v>4</v>
@@ -2659,14 +2659,14 @@
         <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="BG11" t="n">
         <v>5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>7.4</v>
@@ -2721,22 +2721,22 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
         <v>1.93</v>
@@ -2748,7 +2748,7 @@
         <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,10 +2805,10 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
         <v>4</v>
@@ -2817,50 +2817,50 @@
         <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.96</v>
+        <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AW12" t="n">
         <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA12" t="n">
         <v>4.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="G13" t="n">
         <v>2.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="I13" t="n">
         <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2915,16 +2915,16 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
@@ -2939,10 +2939,10 @@
         <v>2.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3014,10 +3014,10 @@
         <v>3.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
         <v>4.6</v>
@@ -3041,7 +3041,7 @@
         <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
         <v>4.8</v>
@@ -3050,11 +3050,11 @@
         <v>3.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.83</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
         <v>4.6</v>
@@ -3127,7 +3127,7 @@
         <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
         <v>2.24</v>
@@ -3136,10 +3136,10 @@
         <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3187,13 +3187,13 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
@@ -3214,7 +3214,7 @@
         <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX14" t="n">
         <v>10</v>
@@ -3235,20 +3235,20 @@
         <v>14</v>
       </c>
       <c r="BD14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
         <v>8.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
         <v>1.93</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
@@ -3306,7 +3306,7 @@
         <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
         <v>2.22</v>
@@ -3318,7 +3318,7 @@
         <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.67</v>
@@ -3399,7 +3399,7 @@
         <v>4.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3435,14 +3435,14 @@
         <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
         <v>4.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>5.3</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.16</v>
@@ -3497,7 +3497,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
         <v>1.1</v>
@@ -3512,7 +3512,7 @@
         <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T16" t="n">
         <v>1.51</v>
@@ -3533,7 +3533,7 @@
         <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
         <v>19.5</v>
@@ -3581,7 +3581,7 @@
         <v>3.75</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -3593,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
@@ -3605,10 +3605,10 @@
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -3617,26 +3617,26 @@
         <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>48</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>34</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
         <v>3.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -3670,97 +3670,97 @@
         <v>6.6</v>
       </c>
       <c r="G17" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="W17" t="n">
         <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA17" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AF17" t="n">
         <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT17" t="n">
         <v>13.5</v>
       </c>
-      <c r="AP17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>15</v>
-      </c>
       <c r="AU17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC17" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -3939,10 +3939,10 @@
         <v>220</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>42</v>
@@ -3963,34 +3963,34 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AO18" t="n">
         <v>170</v>
       </c>
       <c r="AP18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
         <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
         <v>8.6</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
@@ -3999,10 +3999,10 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -4020,11 +4020,11 @@
         <v>2.24</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I19" t="n">
         <v>7.6</v>
-      </c>
-      <c r="I19" t="n">
-        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>4.7</v>
@@ -4082,10 +4082,10 @@
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
         <v>1.89</v>
@@ -4094,31 +4094,31 @@
         <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T19" t="n">
         <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
         <v>65</v>
       </c>
       <c r="AA19" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB19" t="n">
         <v>8.199999999999999</v>
@@ -4127,7 +4127,7 @@
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>120</v>
@@ -4139,13 +4139,13 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK19" t="n">
         <v>15</v>
@@ -4154,25 +4154,25 @@
         <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO19" t="n">
         <v>150</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS19" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -4184,22 +4184,22 @@
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA19" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BB19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
@@ -4214,11 +4214,11 @@
         <v>7.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G20" t="n">
         <v>1.61</v>
@@ -4258,10 +4258,10 @@
         <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K20" t="n">
         <v>5.7</v>
@@ -4279,13 +4279,13 @@
         <v>1.09</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
         <v>1.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S20" t="n">
         <v>1.76</v>
@@ -4297,10 +4297,10 @@
         <v>3.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
         <v>55</v>
@@ -4315,25 +4315,25 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4354,7 +4354,7 @@
         <v>4.1</v>
       </c>
       <c r="AO20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP20" t="n">
         <v>46</v>
@@ -4363,10 +4363,10 @@
         <v>36</v>
       </c>
       <c r="AR20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AT20" t="n">
         <v>21</v>
@@ -4375,7 +4375,7 @@
         <v>15</v>
       </c>
       <c r="AV20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
         <v>42</v>
@@ -4390,7 +4390,7 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
         <v>18.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 07:05:35</t>
+          <t>2026-04-14 09:15:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -772,7 +772,7 @@
         <v>2.94</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -796,7 +796,7 @@
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="T2" t="n">
         <v>1.97</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>2.26</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>5.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>4.7</v>
@@ -990,13 +990,13 @@
         <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
@@ -1154,7 +1154,7 @@
         <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
         <v>2.98</v>
@@ -1166,7 +1166,7 @@
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
         <v>2.72</v>
@@ -1193,10 +1193,10 @@
         <v>1.84</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>11.5</v>
@@ -1232,7 +1232,7 @@
         <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>55</v>
@@ -1271,7 +1271,7 @@
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.3</v>
@@ -1295,10 +1295,10 @@
         <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BF4" t="n">
         <v>8.199999999999999</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1366,13 +1366,13 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
         <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
         <v>1.41</v>
@@ -1381,16 +1381,16 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
         <v>19.5</v>
@@ -1402,7 +1402,7 @@
         <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
@@ -1456,53 +1456,53 @@
         <v>4.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
         <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
         <v>4.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
         <v>9.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>36</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>4.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
         <v>2.04</v>
@@ -1551,7 +1551,7 @@
         <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,16 +1563,16 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
         <v>1.8</v>
@@ -1584,7 +1584,7 @@
         <v>1.97</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>7</v>
@@ -1650,10 +1650,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
@@ -1662,41 +1662,41 @@
         <v>7.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1733,31 +1733,31 @@
         <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
         <v>1.96</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>5.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>4.6</v>
@@ -1945,7 +1945,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.31</v>
@@ -1954,13 +1954,13 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.76</v>
@@ -1969,7 +1969,7 @@
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
         <v>1.9</v>
@@ -2029,7 +2029,7 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8" t="n">
         <v>3.9</v>
@@ -2041,10 +2041,10 @@
         <v>4.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
@@ -2056,7 +2056,7 @@
         <v>3.7</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
         <v>4</v>
@@ -2077,14 +2077,14 @@
         <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG8" t="n">
         <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2148,13 @@
         <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
         <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
         <v>1.84</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>22</v>
+        <v>3.95</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
         <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
         <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.9</v>
       </c>
       <c r="AX10" t="n">
         <v>3.35</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
         <v>3.65</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4</v>
       </c>
-      <c r="BF10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.39</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="H11" t="n">
         <v>7.4</v>
@@ -2518,7 +2518,7 @@
         <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.27</v>
@@ -2554,7 +2554,7 @@
         <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2614,7 +2614,7 @@
         <v>4.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR11" t="n">
         <v>4.9</v>
@@ -2629,7 +2629,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
         <v>5</v>
@@ -2662,11 +2662,11 @@
         <v>4.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -2697,73 +2697,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.84</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
         <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
         <v>11</v>
@@ -2775,11 +2775,11 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG12" t="n">
         <v>12</v>
       </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH12" t="n">
         <v>1000</v>
       </c>
@@ -2787,80 +2787,80 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
         <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
         <v>12.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.95</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H13" t="n">
         <v>3.35</v>
@@ -2903,46 +2903,46 @@
         <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
         <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3011,10 +3011,10 @@
         <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
         <v>4</v>
@@ -3023,7 +3023,7 @@
         <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY13" t="n">
         <v>3.6</v>
@@ -3041,20 +3041,20 @@
         <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
         <v>4.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.15</v>
@@ -3133,10 +3133,10 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="X14" t="n">
         <v>20</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="n">
         <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.29</v>
@@ -3306,19 +3306,19 @@
         <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
         <v>2.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
         <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
         <v>1.67</v>
@@ -3387,7 +3387,7 @@
         <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>16.5</v>
@@ -3399,7 +3399,7 @@
         <v>4.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3423,7 +3423,7 @@
         <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
         <v>13.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>1.16</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
         <v>10</v>
@@ -3503,19 +3503,19 @@
         <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
         <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="T16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U16" t="n">
         <v>2.68</v>
@@ -3530,25 +3530,25 @@
         <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA16" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AB16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF16" t="n">
         <v>100</v>
@@ -3557,10 +3557,10 @@
         <v>38</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
@@ -3578,10 +3578,10 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16" t="n">
         <v>16.5</v>
@@ -3593,10 +3593,10 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -3605,10 +3605,10 @@
         <v>10</v>
       </c>
       <c r="AX16" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -3617,26 +3617,26 @@
         <v>19.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG16" t="n">
         <v>3.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3667,37 +3667,37 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
         <v>7.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
         <v>1.51</v>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
         <v>2.5</v>
@@ -3715,10 +3715,10 @@
         <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>9.800000000000001</v>
@@ -3799,16 +3799,16 @@
         <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
       </c>
       <c r="AZ17" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BA17" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>8.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J18" t="n">
         <v>10</v>
@@ -3879,7 +3879,7 @@
         <v>11.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -3888,19 +3888,19 @@
         <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P18" t="n">
         <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R18" t="n">
         <v>2.42</v>
       </c>
       <c r="S18" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T18" t="n">
         <v>1.76</v>
@@ -3909,22 +3909,22 @@
         <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X18" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y18" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="Z18" t="n">
         <v>210</v>
       </c>
       <c r="AA18" t="n">
-        <v>620</v>
+        <v>570</v>
       </c>
       <c r="AB18" t="n">
         <v>21</v>
@@ -3963,34 +3963,34 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
@@ -3999,10 +3999,10 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
         <v>10</v>
@@ -4014,17 +4014,17 @@
         <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF18" t="n">
         <v>2.24</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.52</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H19" t="n">
         <v>7.4</v>
@@ -4073,49 +4073,49 @@
         <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>1.89</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.9</v>
       </c>
       <c r="V19" t="n">
         <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
         <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="n">
         <v>240</v>
@@ -4127,7 +4127,7 @@
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
         <v>120</v>
@@ -4139,7 +4139,7 @@
         <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>110</v>
@@ -4151,13 +4151,13 @@
         <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO19" t="n">
         <v>150</v>
@@ -4166,16 +4166,16 @@
         <v>15.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AR19" t="n">
         <v>50</v>
       </c>
       <c r="AS19" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
         <v>9.800000000000001</v>
@@ -4184,19 +4184,19 @@
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB19" t="n">
         <v>12.5</v>
@@ -4205,20 +4205,20 @@
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE19" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG19" t="n">
         <v>120</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -4264,7 +4264,7 @@
         <v>5.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.19</v>
@@ -4279,7 +4279,7 @@
         <v>1.09</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q20" t="n">
         <v>1.3</v>
@@ -4303,7 +4303,7 @@
         <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y20" t="n">
         <v>42</v>
@@ -4327,13 +4327,13 @@
         <v>46</v>
       </c>
       <c r="AF20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -4363,16 +4363,16 @@
         <v>36</v>
       </c>
       <c r="AR20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS20" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AT20" t="n">
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AV20" t="n">
         <v>20</v>
@@ -4384,10 +4384,10 @@
         <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 09:15:52</t>
+          <t>2026-04-14 11:23:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,72 +743,72 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.28</v>
+        <v>10.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
-        <v>1.78</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,69 +865,69 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,78 +937,78 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NK Bravo</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>2.68</v>
       </c>
       <c r="G3" t="n">
-        <v>1.94</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="K3" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>1.41</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,34 +1017,34 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,75 +1053,75 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,117 +1131,117 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.72</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1253,69 +1253,69 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Slavia Praha B</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vysocina Jihlava</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W5" t="n">
         <v>2.06</v>
       </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.96</v>
-      </c>
       <c r="X5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sparta Prague B</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>2.68</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.97</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Banik Ostrava B</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>1.23</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>7.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.3</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
         <v>4.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
         <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BD7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>H Slavia Kromeriz</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prostejov</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR8" t="n">
         <v>4.6</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD8" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BE8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>2.26</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,78 +2101,78 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>NK Bravo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,34 +2181,34 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,75 +2217,75 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.3</v>
+        <v>16.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AS9" t="n">
         <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.94</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
         <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BF9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG9" t="n">
         <v>3.95</v>
       </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,117 +2295,117 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Usti nad Labem</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MFK Chrudim</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>2.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="AY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>3.2</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF10" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
@@ -2489,184 +2489,184 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>Slavia Praha B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zizkov</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>2.06</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.27</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.22</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>2.94</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>Sparta Prague B</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ceske Budejovice</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>4.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>1.84</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>1.99</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.26</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT12" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY12" t="n">
         <v>14</v>
       </c>
-      <c r="AR12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Raed (KSA)</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR13" t="n">
         <v>4.2</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AY13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA13" t="n">
         <v>4.6</v>
       </c>
       <c r="BB13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF13" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>3.75</v>
       </c>
       <c r="BG13" t="n">
         <v>4.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,75 +3071,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.04</v>
       </c>
-      <c r="H14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.24</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
         <v>1000</v>
@@ -3151,25 +3151,25 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3187,75 +3187,75 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>4.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BD14" t="n">
         <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="BG14" t="n">
         <v>4.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>1.71</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.01</v>
       </c>
-      <c r="W15" t="n">
+      <c r="BG15" t="n">
         <v>1.01</v>
       </c>
-      <c r="X15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sarpsborg</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>7.8</v>
+        <v>2.48</v>
       </c>
       <c r="H16" t="n">
-        <v>1.44</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
-        <v>1.49</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>10</v>
+        <v>1.86</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>1.79</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,108 +3653,108 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>7.4</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.68</v>
+        <v>2.98</v>
       </c>
       <c r="I17" t="n">
-        <v>1.74</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="V17" t="n">
-        <v>2.34</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="X17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3772,72 +3772,72 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>13.5</v>
+        <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>3.35</v>
       </c>
       <c r="AZ17" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>8.6</v>
+        <v>3.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
         <v>11</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="X18" t="n">
-        <v>95</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>210</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>570</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AR18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>9.4</v>
       </c>
-      <c r="AS18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>10</v>
-      </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.24</v>
+        <v>4.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Usti nad Labem</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>MFK Chrudim</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="H19" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
         <v>3.35</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X19" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>24</v>
+        <v>3.55</v>
       </c>
       <c r="BA19" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>3.65</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>36</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
-        <v>130</v>
+        <v>4.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 11:23:01</t>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,1930 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="J20" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.28</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="X20" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
         <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="n">
         <v>22</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AL20" t="n">
         <v>46</v>
       </c>
-      <c r="AF20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV20" t="n">
         <v>16.5</v>
       </c>
-      <c r="AI20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>20</v>
-      </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>7.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AZ20" t="n">
         <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
       </c>
       <c r="BD20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Czech 2 Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FC Sellier &amp; Bellot Vlasim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FK Pribram</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Saudi 1st Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13:05:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Al-Raed (KSA)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Orubah</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Slovenian Premier League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NK Celje</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Olimpija</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="n">
         <v>18.5</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tromso</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sarpsborg</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Arda</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>19</v>
+      </c>
+      <c r="J27" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>210</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>570</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL28" t="n">
         <v>40</v>
       </c>
-      <c r="BF20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG20" t="n">
+      <c r="AM28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>190</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X29" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG29" t="n">
         <v>22</v>
       </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-04-14 11:23:01</t>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:31:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.2</v>
       </c>
-      <c r="G2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -951,46 +951,46 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J3" t="n">
         <v>2.68</v>
       </c>
-      <c r="G3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P3" t="n">
         <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -999,122 +999,122 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.37</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.51</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>1.41</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.22</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G6" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
         <v>2.56</v>
       </c>
       <c r="I6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.55</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>950</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.44</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G7" t="n">
         <v>1.31</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M7" t="n">
         <v>1.03</v>
       </c>
-      <c r="K7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N7" t="n">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
         <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="X7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AR7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BA7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BB7" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -1930,13 +1930,13 @@
         <v>3.85</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.44</v>
@@ -1960,7 +1960,7 @@
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
         <v>1.97</v>
@@ -1975,7 +1975,7 @@
         <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2032,28 +2032,28 @@
         <v>3.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR8" t="n">
         <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
         <v>4.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AY8" t="n">
         <v>3.65</v>
@@ -2062,7 +2062,7 @@
         <v>4.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB8" t="n">
         <v>4.4</v>
@@ -2074,17 +2074,17 @@
         <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
         <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.26</v>
+        <v>4.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
         <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="n">
         <v>3.95</v>
@@ -2148,7 +2148,7 @@
         <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
         <v>1.54</v>
@@ -2163,7 +2163,7 @@
         <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
         <v>2.16</v>
@@ -2181,19 +2181,19 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
         <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2217,7 +2217,7 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2244,10 +2244,10 @@
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
         <v>7.6</v>
@@ -2256,29 +2256,29 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BF9" t="n">
         <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -2312,13 +2312,13 @@
         <v>2.88</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
         <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -2327,13 +2327,13 @@
         <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
         <v>1.49</v>
@@ -2342,7 +2342,7 @@
         <v>1.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
@@ -2354,10 +2354,10 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
         <v>1.46</v>
@@ -2375,7 +2375,7 @@
         <v>50</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
         <v>970</v>
@@ -2420,59 +2420,59 @@
         <v>8.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
@@ -2542,16 +2542,16 @@
         <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
         <v>1.96</v>
@@ -2623,10 +2623,10 @@
         <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2638,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -2730,7 +2730,7 @@
         <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
@@ -2754,10 +2754,10 @@
         <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2766,10 +2766,10 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2814,22 +2814,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
         <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AV12" t="n">
         <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AY12" t="n">
         <v>14</v>
@@ -2838,29 +2838,29 @@
         <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG12" t="n">
         <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -2900,46 +2900,46 @@
         <v>2.84</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
         <v>1.67</v>
@@ -2960,7 +2960,7 @@
         <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AR13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW13" t="n">
+      <c r="AZ13" t="n">
         <v>4.5</v>
       </c>
-      <c r="AX13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF13" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
         <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.35</v>
@@ -3118,7 +3118,7 @@
         <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
@@ -3133,7 +3133,7 @@
         <v>2.04</v>
       </c>
       <c r="V14" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
         <v>1.9</v>
@@ -3211,7 +3211,7 @@
         <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>4.6</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
         <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
         <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3330,7 +3330,7 @@
         <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>1.86</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>2.98</v>
@@ -3679,7 +3679,7 @@
         <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3691,28 +3691,28 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
         <v>1.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q17" t="n">
         <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
         <v>3.45</v>
       </c>
       <c r="T17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
         <v>1.32</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.39</v>
       </c>
       <c r="G18" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="H18" t="n">
         <v>7.4</v>
@@ -3873,10 +3873,10 @@
         <v>11.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.27</v>
@@ -3885,7 +3885,7 @@
         <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
@@ -3894,13 +3894,13 @@
         <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
         <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
         <v>1.92</v>
@@ -3912,7 +3912,7 @@
         <v>1.09</v>
       </c>
       <c r="W18" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,7 +3969,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>4.6</v>
@@ -4008,7 +4008,7 @@
         <v>9.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
         <v>4.6</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>1.93</v>
       </c>
       <c r="H19" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>5.2</v>
@@ -4094,10 +4094,10 @@
         <v>1.47</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
         <v>2.2</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AS19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AX19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AY19" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.63</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H20" t="n">
         <v>5.5</v>
       </c>
       <c r="I20" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.8</v>
@@ -4267,7 +4267,7 @@
         <v>4.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4288,7 +4288,7 @@
         <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
         <v>1.86</v>
@@ -4297,7 +4297,7 @@
         <v>1.94</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W20" t="n">
         <v>2.28</v>
@@ -4309,7 +4309,7 @@
         <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -4345,7 +4345,7 @@
         <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
@@ -4384,7 +4384,7 @@
         <v>7.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>15.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.83</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT21" t="n">
         <v>7.4</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="G22" t="n">
         <v>2.26</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.33</v>
@@ -4661,34 +4661,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
         <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4748,7 +4748,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
         <v>4.4</v>
@@ -4757,22 +4757,22 @@
         <v>4.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AU22" t="n">
         <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
         <v>4.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>4</v>
@@ -4793,14 +4793,14 @@
         <v>4.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="BG22" t="n">
         <v>4.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -4831,64 +4831,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,25 +4897,25 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4942,59 +4942,59 @@
         <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE23" t="n">
         <v>8</v>
       </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
         <v>4.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.29</v>
@@ -5052,25 +5052,25 @@
         <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R24" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
         <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -5082,55 +5082,55 @@
         <v>23</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC24" t="n">
         <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
       </c>
       <c r="AH24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>21</v>
       </c>
-      <c r="AI24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>23</v>
-      </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM24" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP24" t="n">
         <v>17</v>
@@ -5139,10 +5139,10 @@
         <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT24" t="n">
         <v>9</v>
@@ -5154,7 +5154,7 @@
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
@@ -5166,7 +5166,7 @@
         <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB24" t="n">
         <v>15</v>
@@ -5175,20 +5175,20 @@
         <v>13.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.7</v>
+        <v>60</v>
       </c>
       <c r="BF24" t="n">
         <v>7.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H25" t="n">
         <v>1.44</v>
       </c>
       <c r="I25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="J25" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K25" t="n">
         <v>5.9</v>
@@ -5240,46 +5240,46 @@
         <v>1.16</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="O25" t="n">
         <v>1.1</v>
       </c>
       <c r="P25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R25" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U25" t="n">
         <v>2.68</v>
       </c>
       <c r="V25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Y25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA25" t="n">
         <v>18.5</v>
@@ -5288,22 +5288,22 @@
         <v>60</v>
       </c>
       <c r="AC25" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE25" t="n">
         <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AG25" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>26</v>
@@ -5321,13 +5321,13 @@
         <v>55</v>
       </c>
       <c r="AN25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO25" t="n">
         <v>3.8</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ25" t="n">
         <v>16.5</v>
@@ -5339,7 +5339,7 @@
         <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU25" t="n">
         <v>12.5</v>
@@ -5348,13 +5348,13 @@
         <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AZ25" t="n">
         <v>15</v>
@@ -5363,26 +5363,26 @@
         <v>19.5</v>
       </c>
       <c r="BB25" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD25" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BE25" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>34</v>
+        <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H26" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I26" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,13 +5437,13 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
         <v>2.5</v>
@@ -5452,7 +5452,7 @@
         <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T26" t="n">
         <v>2.3</v>
@@ -5461,22 +5461,22 @@
         <v>1.63</v>
       </c>
       <c r="V26" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="W26" t="n">
         <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y26" t="n">
         <v>6.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AB26" t="n">
         <v>16.5</v>
@@ -5485,13 +5485,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG26" t="n">
         <v>30</v>
@@ -5503,80 +5503,80 @@
         <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AO26" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR26" t="n">
         <v>7.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW26" t="n">
         <v>20</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5622,10 +5622,10 @@
         <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
@@ -5646,7 +5646,7 @@
         <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T27" t="n">
         <v>1.76</v>
@@ -5664,7 +5664,7 @@
         <v>95</v>
       </c>
       <c r="Y27" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Z27" t="n">
         <v>210</v>
@@ -5673,7 +5673,7 @@
         <v>570</v>
       </c>
       <c r="AB27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC27" t="n">
         <v>29</v>
@@ -5685,10 +5685,10 @@
         <v>220</v>
       </c>
       <c r="AF27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
         <v>42</v>
@@ -5697,58 +5697,58 @@
         <v>140</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM27" t="n">
         <v>130</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AO27" t="n">
         <v>160</v>
       </c>
       <c r="AP27" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>11</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ27" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA27" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5757,20 +5757,20 @@
         <v>11.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K28" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.4</v>
@@ -5837,7 +5837,7 @@
         <v>1.95</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
         <v>3.35</v>
@@ -5846,13 +5846,13 @@
         <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X28" t="n">
         <v>15.5</v>
@@ -5861,19 +5861,19 @@
         <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA28" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
         <v>120</v>
@@ -5891,7 +5891,7 @@
         <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK28" t="n">
         <v>16</v>
@@ -5918,7 +5918,7 @@
         <v>50</v>
       </c>
       <c r="AS28" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AT28" t="n">
         <v>7.8</v>
@@ -5927,7 +5927,7 @@
         <v>9.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
         <v>100</v>
@@ -5945,16 +5945,16 @@
         <v>100</v>
       </c>
       <c r="BB28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE28" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BF28" t="n">
         <v>7.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G29" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
         <v>5.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>5.7</v>
@@ -6031,7 +6031,7 @@
         <v>1.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S29" t="n">
         <v>1.75</v>
@@ -6040,10 +6040,10 @@
         <v>1.43</v>
       </c>
       <c r="U29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W29" t="n">
         <v>2.68</v>
@@ -6052,7 +6052,7 @@
         <v>55</v>
       </c>
       <c r="Y29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Z29" t="n">
         <v>60</v>
@@ -6067,7 +6067,7 @@
         <v>16</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>48</v>
@@ -6097,16 +6097,16 @@
         <v>44</v>
       </c>
       <c r="AN29" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AO29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP29" t="n">
         <v>48</v>
       </c>
       <c r="AQ29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AR29" t="n">
         <v>50</v>
@@ -6118,7 +6118,7 @@
         <v>21</v>
       </c>
       <c r="AU29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AV29" t="n">
         <v>21</v>
@@ -6133,7 +6133,7 @@
         <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA29" t="n">
         <v>34</v>
@@ -6154,11 +6154,11 @@
         <v>3.9</v>
       </c>
       <c r="BG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-14 13:31:59</t>
+          <t>2026-04-14 15:42:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -799,22 +799,22 @@
         <v>4.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2" t="n">
         <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
         <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
         <v>11.5</v>
@@ -823,7 +823,7 @@
         <v>22</v>
       </c>
       <c r="AB2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9.6</v>
@@ -865,62 +865,62 @@
         <v>17.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>05:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shenzhen 2028</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xiamen Feilu</t>
+          <t>Xian Chongde Ronghai</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
-        <v>2.56</v>
+        <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="O3" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lanzhou Longyuan Athletic</t>
+          <t>Shenzhen 2028</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shandong Taishan B</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY4" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1330,179 +1330,179 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wenzhou Professional</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hangzhou Linping Wuyue</t>
+          <t>Shandong Taishan B</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.5</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.51</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AR5" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BF5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -1524,70 +1524,70 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns II</t>
+          <t>Wenzhou Professional</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng II</t>
+          <t>Hangzhou Linping Wuyue</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.76</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.56</v>
+        <v>5.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="O6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1611,7 +1611,7 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
@@ -1641,69 +1641,69 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,78 +1713,78 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Wuhan Three Towns II</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeddah Club</t>
+          <t>Chengdu Rongcheng II</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="H7" t="n">
-        <v>11.5</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>5.4</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.03</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2</v>
+        <v>1.44</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,111 +1793,111 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>1.31</v>
       </c>
       <c r="H8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>3.85</v>
       </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>4.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE8" t="n">
         <v>4.7</v>
       </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,78 +2101,78 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NK Bravo</t>
+          <t>Reggina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Enna Calcio</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.84</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.25</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,34 +2181,34 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,75 +2217,75 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
-        <v>2.98</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3.3</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="AV10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.8</v>
       </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AX10" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Slavia Praha B</t>
+          <t>NK Bravo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vysocina Jihlava</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sparta Prague B</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
         <v>4.3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="T12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX12" t="n">
         <v>4.9</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AY12" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>5.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Banik Ostrava B</t>
+          <t>Slavia Praha B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SFC Opava</t>
+          <t>Vysocina Jihlava</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.42</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
         <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE13" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BF13" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -3076,100 +3076,100 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H Slavia Kromeriz</t>
+          <t>Sparta Prague B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prostejov</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>4.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>1.99</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
         <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3190,72 +3190,72 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.7</v>
+        <v>16.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Faisaly ( KSA )</t>
+          <t>Banik Ostrava B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Taee</t>
+          <t>SFC Opava</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.67</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU15" t="n">
         <v>6.4</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>H Slavia Kromeriz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al-Arabi Al-Saudi</t>
+          <t>Prostejov</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>1.76</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.03</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,67 +3658,67 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CSA Steaua Bucuresti</t>
+          <t>Al Faisaly ( KSA )</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="H17" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="W17" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,69 +3775,69 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,67 +3852,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FC Zbrojovka Brno</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zizkov</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.27</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>3.05</v>
+        <v>1.66</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3927,7 +3927,7 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
         <v>1000</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
@@ -3963,75 +3963,75 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW18" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA18" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BB18" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Usti nad Labem</t>
+          <t>CSA Steaua Bucuresti</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MFK Chrudim</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I19" t="n">
         <v>4.1</v>
       </c>
-      <c r="I19" t="n">
-        <v>5.6</v>
-      </c>
       <c r="J19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV19" t="n">
         <v>3.8</v>
       </c>
-      <c r="K19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AW19" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>2.72</v>
-      </c>
       <c r="AX19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="AZ19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="BF19" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -4240,70 +4240,70 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Zbrojovka Brno</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceske Budejovice</t>
+          <t>Zizkov</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="G20" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="H20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" t="n">
         <v>5.5</v>
       </c>
-      <c r="I20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.03</v>
       </c>
       <c r="V20" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="X20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
         <v>1000</v>
@@ -4315,19 +4315,19 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -4339,10 +4339,10 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB20" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FC Sellier &amp; Bellot Vlasim</t>
+          <t>Usti nad Labem</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Pribram</t>
+          <t>MFK Chrudim</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U21" t="n">
         <v>2.2</v>
       </c>
-      <c r="H21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>4.8</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="AQ21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AX21" t="n">
         <v>4.1</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS21" t="n">
+      <c r="AY21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BB21" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,78 +4623,78 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Al-Raed (KSA)</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Ceske Budejovice</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="G22" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,111 +4703,111 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV22" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT22" t="n">
+      <c r="AW22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AU22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD22" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>FC Sellier &amp; Bellot Vlasim</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>FK Pribram</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
         <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
         <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
         <v>4.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="X23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY23" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:05:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tromso</t>
+          <t>Al-Raed (KSA)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.05</v>
       </c>
-      <c r="N24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="U24" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sarpsborg</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="G25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW25" t="n">
         <v>7.8</v>
       </c>
-      <c r="H25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AX25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF25" t="n">
         <v>11</v>
       </c>
-      <c r="AS25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Tromso</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>1.86</v>
       </c>
       <c r="G26" t="n">
-        <v>7.6</v>
+        <v>1.96</v>
       </c>
       <c r="H26" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.69</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>2.68</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.3</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.63</v>
-      </c>
       <c r="V26" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="AA26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
         <v>18</v>
       </c>
-      <c r="AB26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AI26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>320</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>310</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU26" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AV26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC26" t="n">
         <v>15</v>
       </c>
-      <c r="AT26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>27</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>11</v>
-      </c>
       <c r="BD26" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BF26" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Sarpsborg</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.17</v>
+        <v>6.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>14.5</v>
+        <v>1.44</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>1.46</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P27" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>2.7</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="Y27" t="n">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>210</v>
+        <v>16</v>
       </c>
       <c r="AA27" t="n">
-        <v>570</v>
+        <v>17.5</v>
       </c>
       <c r="AB27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA27" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="BB27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE27" t="n">
         <v>42</v>
       </c>
-      <c r="AI27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>11</v>
-      </c>
       <c r="BF27" t="n">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting Lisbon</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H28" t="n">
         <v>1.55</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Z28" t="n">
         <v>7.6</v>
       </c>
-      <c r="I28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>65</v>
-      </c>
       <c r="AA28" t="n">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="AF28" t="n">
-        <v>8.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="AG28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>450</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>520</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV28" t="n">
         <v>10</v>
       </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>200</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>27</v>
-      </c>
       <c r="AW28" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA28" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="BB28" t="n">
         <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>130</v>
+        <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-14 15:42:20</t>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,766 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>5.8</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="M29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P29" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="R29" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S29" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="T29" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="U29" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>2.68</v>
+        <v>6</v>
       </c>
       <c r="X29" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="Y29" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="Z29" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AA29" t="n">
-        <v>130</v>
+        <v>630</v>
       </c>
       <c r="AB29" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AE29" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="AF29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK29" t="n">
         <v>13.5</v>
       </c>
       <c r="AL29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-14 17:49:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>19.5</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AK30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW30" t="n">
         <v>44</v>
       </c>
-      <c r="AN29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AO29" t="n">
+      <c r="AX30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-14 17:49:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sporting Lisbon</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>25</v>
       </c>
-      <c r="AP29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AQ29" t="n">
+      <c r="BA31" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD31" t="n">
         <v>36</v>
       </c>
-      <c r="AR29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-04-14 15:42:20</t>
+      <c r="BE31" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>130</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-14 17:49:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Juticalpa</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Platense FC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>950</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-14 17:49:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,766 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Juticalpa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 17:24:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sporting Lisbon</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S3" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>380</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>240</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>460</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>130</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>270</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>400</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:24:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:24:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Honduras Liga Nacional</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Juticalpa</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Platense FC</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-04-15 17:24:47</t>
+          <t>2026-04-15 19:37:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-15.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G2" t="n">
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -781,7 +781,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
@@ -790,22 +790,22 @@
         <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="T2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
@@ -814,55 +814,55 @@
         <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>11</v>
       </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
       <c r="AE2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP2" t="n">
         <v>15.5</v>
@@ -889,7 +889,7 @@
         <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>46</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.2</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-15 19:37:38</t>
+          <t>2026-04-15 21:51:30</t>
         </is>
       </c>
     </row>
